--- a/Docs/TitraSimsProposeTimeline.xlsx
+++ b/Docs/TitraSimsProposeTimeline.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ryzen\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Others\Unity\TitraSims\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DCE36B6-0469-40F5-AD57-6880F77F7BEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2F2D1BE-8D33-4E77-B425-5890AB332965}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{0CA07CFE-78C6-4054-9F6F-B6E069F5232C}"/>
   </bookViews>
@@ -331,7 +331,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -362,6 +362,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -489,9 +495,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -529,6 +532,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -857,24 +863,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
     </row>
     <row r="3" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -969,14 +975,14 @@
       <c r="P4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="S4" s="19"/>
-      <c r="T4" s="19" t="s">
+      <c r="S4" s="18"/>
+      <c r="T4" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="U4" s="19" t="s">
+      <c r="U4" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="V4" s="19" t="s">
+      <c r="V4" s="18" t="s">
         <v>75</v>
       </c>
     </row>
@@ -999,17 +1005,17 @@
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
-      <c r="S5" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="T5" s="21">
+      <c r="S5" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="T5" s="20">
         <f>SUMIF(B6:B43, "Kevin", C6:C43)</f>
         <v>167</v>
       </c>
-      <c r="U5" s="22">
+      <c r="U5" s="21">
         <v>90000</v>
       </c>
-      <c r="V5" s="22">
+      <c r="V5" s="21">
         <f>T5*U5</f>
         <v>15030000</v>
       </c>
@@ -1024,32 +1030,32 @@
       <c r="C6" s="13">
         <v>4</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="27">
         <v>4</v>
       </c>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="16"/>
-      <c r="N6" s="16"/>
-      <c r="O6" s="16"/>
-      <c r="P6" s="16"/>
-      <c r="S6" s="23" t="s">
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
+      <c r="P6" s="15"/>
+      <c r="S6" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="T6" s="24">
+      <c r="T6" s="23">
         <f>87-27</f>
         <v>60</v>
       </c>
-      <c r="U6" s="22">
+      <c r="U6" s="21">
         <v>75000</v>
       </c>
-      <c r="V6" s="22">
+      <c r="V6" s="21">
         <f>T6*U6</f>
         <v>4500000</v>
       </c>
@@ -1064,30 +1070,30 @@
       <c r="C7" s="13">
         <v>12</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="27">
         <v>8</v>
       </c>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="16"/>
-      <c r="O7" s="16"/>
-      <c r="P7" s="16"/>
-      <c r="S7" s="19" t="s">
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="15"/>
+      <c r="O7" s="15"/>
+      <c r="P7" s="15"/>
+      <c r="S7" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="T7" s="19">
+      <c r="T7" s="18">
         <f xml:space="preserve"> SUM(T5:T6)</f>
         <v>227</v>
       </c>
-      <c r="U7" s="22"/>
-      <c r="V7" s="22">
+      <c r="U7" s="21"/>
+      <c r="V7" s="21">
         <f t="shared" ref="V7" si="0" xml:space="preserve"> SUM(V5:V6)</f>
         <v>19530000</v>
       </c>
@@ -1102,21 +1108,21 @@
       <c r="C8" s="13">
         <v>2</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="27">
         <v>2</v>
       </c>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="16"/>
-      <c r="O8" s="16"/>
-      <c r="P8" s="16"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="15"/>
+      <c r="O8" s="15"/>
+      <c r="P8" s="15"/>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
@@ -1128,21 +1134,21 @@
       <c r="C9" s="13">
         <v>2</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="27">
         <v>2</v>
       </c>
-      <c r="E9" s="15"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="16"/>
-      <c r="O9" s="16"/>
-      <c r="P9" s="16"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="15"/>
+      <c r="O9" s="15"/>
+      <c r="P9" s="15"/>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
@@ -1157,38 +1163,38 @@
       <c r="D10" s="9">
         <v>10</v>
       </c>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="16"/>
-      <c r="P10" s="16"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15"/>
+      <c r="P10" s="15"/>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B11" s="12"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
-      <c r="N11" s="17"/>
-      <c r="O11" s="17"/>
-      <c r="P11" s="17"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="16"/>
+      <c r="O11" s="16"/>
+      <c r="P11" s="16"/>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
@@ -1200,21 +1206,21 @@
       <c r="C12" s="13">
         <v>8</v>
       </c>
-      <c r="D12" s="16"/>
+      <c r="D12" s="15"/>
       <c r="E12" s="6">
         <v>8</v>
       </c>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="16"/>
-      <c r="O12" s="16"/>
-      <c r="P12" s="16"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="15"/>
+      <c r="O12" s="15"/>
+      <c r="P12" s="15"/>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
@@ -1226,21 +1232,21 @@
       <c r="C13" s="13">
         <v>5</v>
       </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
       <c r="F13" s="6">
         <v>5</v>
       </c>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="16"/>
-      <c r="O13" s="16"/>
-      <c r="P13" s="16"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="15"/>
+      <c r="O13" s="15"/>
+      <c r="P13" s="15"/>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
@@ -1252,21 +1258,21 @@
       <c r="C14" s="13">
         <v>8</v>
       </c>
-      <c r="D14" s="16"/>
+      <c r="D14" s="15"/>
       <c r="E14" s="6">
         <v>8</v>
       </c>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="16"/>
-      <c r="O14" s="16"/>
-      <c r="P14" s="16"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="15"/>
+      <c r="O14" s="15"/>
+      <c r="P14" s="15"/>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
@@ -1278,21 +1284,21 @@
       <c r="C15" s="13">
         <v>6</v>
       </c>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
       <c r="F15" s="6">
         <v>6</v>
       </c>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="16"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="16"/>
-      <c r="O15" s="16"/>
-      <c r="P15" s="16"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="15"/>
+      <c r="O15" s="15"/>
+      <c r="P15" s="15"/>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -1304,21 +1310,21 @@
       <c r="C16" s="13">
         <v>4</v>
       </c>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
       <c r="F16" s="6">
         <v>4</v>
       </c>
-      <c r="G16" s="16"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="16"/>
-      <c r="O16" s="16"/>
-      <c r="P16" s="16"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="15"/>
+      <c r="O16" s="15"/>
+      <c r="P16" s="15"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
@@ -1330,21 +1336,21 @@
       <c r="C17" s="13">
         <v>6</v>
       </c>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
       <c r="F17" s="6">
         <v>6</v>
       </c>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="16"/>
-      <c r="O17" s="16"/>
-      <c r="P17" s="16"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="15"/>
+      <c r="O17" s="15"/>
+      <c r="P17" s="15"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
@@ -1353,24 +1359,24 @@
       <c r="B18" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="16">
+      <c r="C18" s="15">
         <v>5</v>
       </c>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="18">
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="17">
         <v>5</v>
       </c>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="16"/>
-      <c r="O18" s="16"/>
-      <c r="P18" s="16"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+      <c r="N18" s="15"/>
+      <c r="O18" s="15"/>
+      <c r="P18" s="15"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
@@ -1379,44 +1385,44 @@
       <c r="B19" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="C19" s="16">
+      <c r="C19" s="15">
         <v>5</v>
       </c>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="18">
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="17">
         <v>5</v>
       </c>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="16"/>
-      <c r="O19" s="16"/>
-      <c r="P19" s="16"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="15"/>
+      <c r="N19" s="15"/>
+      <c r="O19" s="15"/>
+      <c r="P19" s="15"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>45</v>
       </c>
       <c r="B20" s="12"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="17"/>
-      <c r="L20" s="17"/>
-      <c r="M20" s="17"/>
-      <c r="N20" s="17"/>
-      <c r="O20" s="17"/>
-      <c r="P20" s="17"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="16"/>
+      <c r="K20" s="16"/>
+      <c r="L20" s="16"/>
+      <c r="M20" s="16"/>
+      <c r="N20" s="16"/>
+      <c r="O20" s="16"/>
+      <c r="P20" s="16"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
@@ -1428,21 +1434,21 @@
       <c r="C21" s="13">
         <v>7</v>
       </c>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
       <c r="G21" s="6">
         <v>7</v>
       </c>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="16"/>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="16"/>
-      <c r="O21" s="16"/>
-      <c r="P21" s="16"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="15"/>
+      <c r="N21" s="15"/>
+      <c r="O21" s="15"/>
+      <c r="P21" s="15"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
@@ -1454,21 +1460,21 @@
       <c r="C22" s="13">
         <v>6</v>
       </c>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
       <c r="G22" s="6">
         <v>6</v>
       </c>
-      <c r="H22" s="16"/>
-      <c r="I22" s="16"/>
-      <c r="J22" s="16"/>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="16"/>
-      <c r="O22" s="16"/>
-      <c r="P22" s="16"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="15"/>
+      <c r="O22" s="15"/>
+      <c r="P22" s="15"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
@@ -1480,21 +1486,21 @@
       <c r="C23" s="13">
         <v>8</v>
       </c>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
       <c r="H23" s="6">
         <v>8</v>
       </c>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="16"/>
-      <c r="O23" s="16"/>
-      <c r="P23" s="16"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="15"/>
+      <c r="O23" s="15"/>
+      <c r="P23" s="15"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
@@ -1506,21 +1512,21 @@
       <c r="C24" s="13">
         <v>3</v>
       </c>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
       <c r="G24" s="6">
         <v>3</v>
       </c>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="16"/>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="16"/>
-      <c r="O24" s="16"/>
-      <c r="P24" s="16"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="15"/>
+      <c r="J24" s="15"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="15"/>
+      <c r="M24" s="15"/>
+      <c r="N24" s="15"/>
+      <c r="O24" s="15"/>
+      <c r="P24" s="15"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
@@ -1532,21 +1538,21 @@
       <c r="C25" s="13">
         <v>9</v>
       </c>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
       <c r="H25" s="6">
         <v>9</v>
       </c>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="16"/>
-      <c r="O25" s="16"/>
-      <c r="P25" s="16"/>
+      <c r="I25" s="15"/>
+      <c r="J25" s="15"/>
+      <c r="K25" s="15"/>
+      <c r="L25" s="15"/>
+      <c r="M25" s="15"/>
+      <c r="N25" s="15"/>
+      <c r="O25" s="15"/>
+      <c r="P25" s="15"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
@@ -1558,21 +1564,21 @@
       <c r="C26" s="13">
         <v>7</v>
       </c>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
       <c r="I26" s="6">
         <v>7</v>
       </c>
-      <c r="J26" s="16"/>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="16"/>
-      <c r="O26" s="16"/>
-      <c r="P26" s="16"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="15"/>
+      <c r="L26" s="15"/>
+      <c r="M26" s="15"/>
+      <c r="N26" s="15"/>
+      <c r="O26" s="15"/>
+      <c r="P26" s="15"/>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
@@ -1584,21 +1590,21 @@
       <c r="C27" s="13">
         <v>9</v>
       </c>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
       <c r="I27" s="6">
         <v>9</v>
       </c>
-      <c r="J27" s="16"/>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="16"/>
-      <c r="O27" s="16"/>
-      <c r="P27" s="16"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="15"/>
+      <c r="N27" s="15"/>
+      <c r="O27" s="15"/>
+      <c r="P27" s="15"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
@@ -1610,21 +1616,21 @@
       <c r="C28" s="13">
         <v>22</v>
       </c>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="16"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="15"/>
       <c r="J28" s="9">
         <v>22</v>
       </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="16"/>
-      <c r="O28" s="16"/>
-      <c r="P28" s="16"/>
+      <c r="K28" s="15"/>
+      <c r="L28" s="15"/>
+      <c r="M28" s="15"/>
+      <c r="N28" s="15"/>
+      <c r="O28" s="15"/>
+      <c r="P28" s="15"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
@@ -1636,41 +1642,41 @@
       <c r="C29" s="13">
         <v>8</v>
       </c>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="16"/>
-      <c r="I29" s="16"/>
-      <c r="J29" s="16"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="15"/>
+      <c r="J29" s="15"/>
       <c r="K29" s="9">
         <v>8</v>
       </c>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="16"/>
-      <c r="O29" s="16"/>
-      <c r="P29" s="16"/>
+      <c r="L29" s="15"/>
+      <c r="M29" s="15"/>
+      <c r="N29" s="15"/>
+      <c r="O29" s="15"/>
+      <c r="P29" s="15"/>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>55</v>
       </c>
       <c r="B30" s="12"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17"/>
-      <c r="I30" s="17"/>
-      <c r="J30" s="17"/>
-      <c r="K30" s="17"/>
-      <c r="L30" s="17"/>
-      <c r="M30" s="17"/>
-      <c r="N30" s="17"/>
-      <c r="O30" s="17"/>
-      <c r="P30" s="17"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="16"/>
+      <c r="I30" s="16"/>
+      <c r="J30" s="16"/>
+      <c r="K30" s="16"/>
+      <c r="L30" s="16"/>
+      <c r="M30" s="16"/>
+      <c r="N30" s="16"/>
+      <c r="O30" s="16"/>
+      <c r="P30" s="16"/>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
@@ -1682,21 +1688,21 @@
       <c r="C31" s="13">
         <v>8</v>
       </c>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="15"/>
       <c r="I31" s="6">
         <v>8</v>
       </c>
-      <c r="J31" s="16"/>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="16"/>
-      <c r="O31" s="16"/>
-      <c r="P31" s="16"/>
+      <c r="J31" s="15"/>
+      <c r="K31" s="15"/>
+      <c r="L31" s="15"/>
+      <c r="M31" s="15"/>
+      <c r="N31" s="15"/>
+      <c r="O31" s="15"/>
+      <c r="P31" s="15"/>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
@@ -1708,21 +1714,21 @@
       <c r="C32" s="13">
         <v>12</v>
       </c>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="16"/>
-      <c r="I32" s="16"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="15"/>
       <c r="J32" s="6">
         <v>12</v>
       </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="16"/>
-      <c r="O32" s="16"/>
-      <c r="P32" s="16"/>
+      <c r="K32" s="15"/>
+      <c r="L32" s="15"/>
+      <c r="M32" s="15"/>
+      <c r="N32" s="15"/>
+      <c r="O32" s="15"/>
+      <c r="P32" s="15"/>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
@@ -1734,21 +1740,21 @@
       <c r="C33" s="13">
         <v>9</v>
       </c>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="16"/>
-      <c r="H33" s="16"/>
-      <c r="I33" s="16"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
       <c r="J33" s="6">
         <v>9</v>
       </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="16"/>
-      <c r="O33" s="16"/>
-      <c r="P33" s="16"/>
+      <c r="K33" s="15"/>
+      <c r="L33" s="15"/>
+      <c r="M33" s="15"/>
+      <c r="N33" s="15"/>
+      <c r="O33" s="15"/>
+      <c r="P33" s="15"/>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
@@ -1760,21 +1766,21 @@
       <c r="C34" s="13">
         <v>3</v>
       </c>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
-      <c r="H34" s="16"/>
-      <c r="I34" s="16"/>
-      <c r="J34" s="16"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="15"/>
+      <c r="I34" s="15"/>
+      <c r="J34" s="15"/>
       <c r="K34" s="6">
         <v>3</v>
       </c>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="16"/>
-      <c r="O34" s="16"/>
-      <c r="P34" s="16"/>
+      <c r="L34" s="15"/>
+      <c r="M34" s="15"/>
+      <c r="N34" s="15"/>
+      <c r="O34" s="15"/>
+      <c r="P34" s="15"/>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
@@ -1786,21 +1792,21 @@
       <c r="C35" s="13">
         <v>9</v>
       </c>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="16"/>
-      <c r="H35" s="16"/>
-      <c r="I35" s="16"/>
-      <c r="J35" s="16"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="15"/>
+      <c r="J35" s="15"/>
       <c r="K35" s="6">
         <v>9</v>
       </c>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="16"/>
-      <c r="O35" s="16"/>
-      <c r="P35" s="16"/>
+      <c r="L35" s="15"/>
+      <c r="M35" s="15"/>
+      <c r="N35" s="15"/>
+      <c r="O35" s="15"/>
+      <c r="P35" s="15"/>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
@@ -1812,21 +1818,21 @@
       <c r="C36" s="13">
         <v>4</v>
       </c>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="16"/>
-      <c r="H36" s="16"/>
-      <c r="I36" s="16"/>
-      <c r="J36" s="16"/>
-      <c r="K36" s="16"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="15"/>
+      <c r="J36" s="15"/>
+      <c r="K36" s="15"/>
       <c r="L36" s="6">
         <v>4</v>
       </c>
-      <c r="M36" s="16"/>
-      <c r="N36" s="16"/>
-      <c r="O36" s="16"/>
-      <c r="P36" s="16"/>
+      <c r="M36" s="15"/>
+      <c r="N36" s="15"/>
+      <c r="O36" s="15"/>
+      <c r="P36" s="15"/>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
@@ -1838,21 +1844,21 @@
       <c r="C37" s="13">
         <v>6</v>
       </c>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="16"/>
-      <c r="G37" s="16"/>
-      <c r="H37" s="16"/>
-      <c r="I37" s="16"/>
-      <c r="J37" s="16"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="15"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="15"/>
+      <c r="I37" s="15"/>
+      <c r="J37" s="15"/>
       <c r="K37" s="6">
         <v>6</v>
       </c>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="16"/>
-      <c r="O37" s="16"/>
-      <c r="P37" s="16"/>
+      <c r="L37" s="15"/>
+      <c r="M37" s="15"/>
+      <c r="N37" s="15"/>
+      <c r="O37" s="15"/>
+      <c r="P37" s="15"/>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
@@ -1864,21 +1870,21 @@
       <c r="C38" s="13">
         <v>2</v>
       </c>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
-      <c r="H38" s="16"/>
-      <c r="I38" s="16"/>
-      <c r="J38" s="16"/>
-      <c r="K38" s="16"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="15"/>
+      <c r="J38" s="15"/>
+      <c r="K38" s="15"/>
       <c r="L38" s="9">
         <v>2</v>
       </c>
-      <c r="M38" s="16"/>
-      <c r="N38" s="16"/>
-      <c r="O38" s="16"/>
-      <c r="P38" s="16"/>
+      <c r="M38" s="15"/>
+      <c r="N38" s="15"/>
+      <c r="O38" s="15"/>
+      <c r="P38" s="15"/>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
@@ -1890,41 +1896,41 @@
       <c r="C39" s="13">
         <v>2</v>
       </c>
-      <c r="D39" s="16"/>
-      <c r="E39" s="16"/>
-      <c r="F39" s="16"/>
-      <c r="G39" s="16"/>
-      <c r="H39" s="16"/>
-      <c r="I39" s="16"/>
-      <c r="J39" s="16"/>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="15"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="15"/>
+      <c r="I39" s="15"/>
+      <c r="J39" s="15"/>
+      <c r="K39" s="15"/>
+      <c r="L39" s="15"/>
       <c r="M39" s="9">
         <v>2</v>
       </c>
-      <c r="N39" s="16"/>
-      <c r="O39" s="16"/>
-      <c r="P39" s="16"/>
+      <c r="N39" s="15"/>
+      <c r="O39" s="15"/>
+      <c r="P39" s="15"/>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>65</v>
       </c>
       <c r="B40" s="12"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="17"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="17"/>
-      <c r="G40" s="17"/>
-      <c r="H40" s="17"/>
-      <c r="I40" s="17"/>
-      <c r="J40" s="17"/>
-      <c r="K40" s="17"/>
-      <c r="L40" s="17"/>
-      <c r="M40" s="17"/>
-      <c r="N40" s="17"/>
-      <c r="O40" s="17"/>
-      <c r="P40" s="17"/>
+      <c r="C40" s="16"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="16"/>
+      <c r="G40" s="16"/>
+      <c r="H40" s="16"/>
+      <c r="I40" s="16"/>
+      <c r="J40" s="16"/>
+      <c r="K40" s="16"/>
+      <c r="L40" s="16"/>
+      <c r="M40" s="16"/>
+      <c r="N40" s="16"/>
+      <c r="O40" s="16"/>
+      <c r="P40" s="16"/>
     </row>
     <row r="41" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
@@ -1936,14 +1942,14 @@
       <c r="C41" s="13">
         <v>32</v>
       </c>
-      <c r="D41" s="16"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="16"/>
-      <c r="G41" s="16"/>
-      <c r="H41" s="16"/>
-      <c r="I41" s="16"/>
-      <c r="J41" s="16"/>
-      <c r="K41" s="16"/>
+      <c r="D41" s="15"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="15"/>
+      <c r="H41" s="15"/>
+      <c r="I41" s="15"/>
+      <c r="J41" s="15"/>
+      <c r="K41" s="15"/>
       <c r="L41" s="6">
         <v>8</v>
       </c>
@@ -1956,7 +1962,7 @@
       <c r="O41" s="6">
         <v>8</v>
       </c>
-      <c r="P41" s="16"/>
+      <c r="P41" s="15"/>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
@@ -1968,21 +1974,21 @@
       <c r="C42" s="13">
         <v>5</v>
       </c>
-      <c r="D42" s="16"/>
-      <c r="E42" s="16"/>
-      <c r="F42" s="16"/>
-      <c r="G42" s="16"/>
-      <c r="H42" s="16"/>
-      <c r="I42" s="16"/>
-      <c r="J42" s="16"/>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="16"/>
+      <c r="D42" s="15"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="15"/>
+      <c r="H42" s="15"/>
+      <c r="I42" s="15"/>
+      <c r="J42" s="15"/>
+      <c r="K42" s="15"/>
+      <c r="L42" s="15"/>
+      <c r="M42" s="15"/>
+      <c r="N42" s="15"/>
       <c r="O42" s="9">
         <v>5</v>
       </c>
-      <c r="P42" s="16"/>
+      <c r="P42" s="15"/>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
@@ -1994,32 +2000,32 @@
       <c r="C43" s="13">
         <v>6</v>
       </c>
-      <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
-      <c r="F43" s="16"/>
-      <c r="G43" s="16"/>
-      <c r="H43" s="16"/>
-      <c r="I43" s="16"/>
-      <c r="J43" s="16"/>
-      <c r="K43" s="16"/>
+      <c r="D43" s="15"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="15"/>
+      <c r="G43" s="15"/>
+      <c r="H43" s="15"/>
+      <c r="I43" s="15"/>
+      <c r="J43" s="15"/>
+      <c r="K43" s="15"/>
       <c r="L43" s="6">
         <v>3</v>
       </c>
       <c r="M43" s="6">
         <v>3</v>
       </c>
-      <c r="N43" s="16"/>
-      <c r="O43" s="16"/>
-      <c r="P43" s="16"/>
+      <c r="N43" s="15"/>
+      <c r="O43" s="15"/>
+      <c r="P43" s="15"/>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" s="25" t="s">
+      <c r="A44" s="24" t="s">
         <v>77</v>
       </c>
       <c r="B44" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="C44" s="26">
+      <c r="C44" s="25">
         <v>2</v>
       </c>
       <c r="O44" s="6">
